--- a/knowledge_base/source/11_scoring_policy.xlsx
+++ b/knowledge_base/source/11_scoring_policy.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_scoring_policy" sheetId="1" r:id="R70943c31e5894778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_scoring_policy" sheetId="1" r:id="R16f6ca7714d048f8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -269,6 +269,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1162,10 +1163,33 @@
         <x:v>The rules and outputs should be reviewed using representative exams before institutional deployment.</x:v>
       </x:c>
     </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="30" t="str">
+        <x:v>SCORE031</x:v>
+      </x:c>
+      <x:c r="B32" s="30" t="str">
+        <x:v>Recommendation Policy</x:v>
+      </x:c>
+      <x:c r="C32" s="30" t="str">
+        <x:v>Deduplicate Identical Recommendations</x:v>
+      </x:c>
+      <x:c r="D32" s="30" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="E32" s="30" t="str">
+        <x:v>Report and Recommendations</x:v>
+      </x:c>
+      <x:c r="F32" s="30" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="G32" s="30" t="str">
+        <x:v>Separate findings remain visible, but the same controlled recommendation is displayed only once in the consolidated recommendations section.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3645e9fda28643eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a263be5527e446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>